--- a/ZAC_zzx/results/fourway/四方法对比_硬层.xlsx
+++ b/ZAC_zzx/results/fourway/四方法对比_硬层.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,8 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,80 +483,90 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Num. Layers</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Max 2Q-Gates in Layer</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>ZAC Steps</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>ICCAD Steps</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>遗传(无前瞻) Steps</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>遗传(前瞻) Steps</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>ZAC move μs</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>ICCAD move μs</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>遗传(无前瞻) move</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>遗传(前瞻) move</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>ZAC fid</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>ICCAD fid</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>遗传(无前瞻) fid</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>遗传(前瞻) fid</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>ZAC 编译s</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>ICCAD 编译s</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>遗传(无前瞻) 编译s</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>遗传(前瞻) 编译s</t>
         </is>
@@ -573,51 +585,57 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>26</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>26</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>27</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>27</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>2768.6</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>2781.7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>3310.7</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>3310.7</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.8572</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.838008</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.8512</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.8512</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>5.09</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.02</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.29</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -634,51 +652,57 @@
         <v>18</v>
       </c>
       <c r="D4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>37</v>
-      </c>
-      <c r="E4" t="n">
-        <v>36</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36</v>
       </c>
       <c r="G4" t="n">
         <v>36</v>
       </c>
       <c r="H4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J4" t="n">
         <v>3945.2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>3812.3</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>4510</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>4510</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.7977</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.767308</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.7938</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.7938</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>5.3</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.02</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -695,51 +719,57 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>37</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>36</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>35</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>35</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>4065.9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>4120.4</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>4069.1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>4069.1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.7727000000000001</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.715657</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.776</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.776</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>3.47</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.02</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.5</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -756,51 +786,57 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>73</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>77</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>71</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>71</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>9053.1</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>8572.200000000001</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>8777.799999999999</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>8777.799999999999</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.4517</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.321849</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.4656</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.4656</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.03</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>1.4</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -817,51 +853,57 @@
         <v>21</v>
       </c>
       <c r="D7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>43</v>
-      </c>
-      <c r="E7" t="n">
-        <v>42</v>
-      </c>
-      <c r="F7" t="n">
-        <v>42</v>
       </c>
       <c r="G7" t="n">
         <v>42</v>
       </c>
       <c r="H7" t="n">
+        <v>42</v>
+      </c>
+      <c r="I7" t="n">
+        <v>42</v>
+      </c>
+      <c r="J7" t="n">
         <v>4597.8</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>4489.8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>5122.6</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>5122.6</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.7621</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.73875</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.7578</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.7578</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>6.56</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.02</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -878,51 +920,57 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>69</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>69</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>67</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>67</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>8173.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>7489.8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>8312.1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>8312.1</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.5949</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.551554</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.5955</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.5955</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>6.84</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.02</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1.1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -939,51 +987,57 @@
         <v>22</v>
       </c>
       <c r="D9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
         <v>44</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>44</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>43</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>43</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>4736.7</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>4736.7</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>5264.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>5264.9</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.7509</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.7245470000000001</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.7479</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.7479</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>6.54</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.02</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>0.54</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -1000,51 +1054,57 @@
         <v>39</v>
       </c>
       <c r="D10" t="n">
+        <v>39</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>78</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>79</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>77</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>77</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>9616.700000000001</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>8518.700000000001</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>9541.200000000001</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>9541.200000000001</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.5309</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.486111</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.5343</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.5343</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>6.93</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.03</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>1.37</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>1.37</v>
       </c>
     </row>
@@ -1061,51 +1121,57 @@
         <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>154</v>
       </c>
       <c r="G11" t="n">
+        <v>157</v>
+      </c>
+      <c r="H11" t="n">
         <v>154</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
+        <v>154</v>
+      </c>
+      <c r="J11" t="n">
         <v>17905.9</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>17202.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>19291.3</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>19291.3</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.1833</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.124179</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.1745</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.1745</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>7.23</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.05</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>3.13</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>3.17</v>
       </c>
     </row>
@@ -1122,51 +1188,57 @@
         <v>82</v>
       </c>
       <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F12" t="n">
         <v>22</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>8</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>24</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>24</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>3115.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1316.9</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>3459</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>3494.7</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.4566</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.371456</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.4911</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.4906</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>6.96</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.04</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>3.08</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>3.22</v>
       </c>
     </row>
@@ -1183,51 +1255,57 @@
         <v>194</v>
       </c>
       <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>49</v>
+      </c>
+      <c r="F13" t="n">
         <v>23</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>13</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>29</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>31</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>3233.4</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>1820</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>4785.1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>4661.7</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.1553</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.053335</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.1693</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.171</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>7.13</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.1</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>27.86</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>26.37</v>
       </c>
     </row>
@@ -1244,51 +1322,57 @@
         <v>120</v>
       </c>
       <c r="D14" t="n">
+        <v>77</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
         <v>157</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>153</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>95</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>95</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>16400.7</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>16002.7</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>10982</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>10982</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.2513</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.186974</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.3474</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.3474</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>8.68</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.06</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>4.51</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>4.51</v>
       </c>
     </row>
@@ -1305,51 +1389,57 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
         <v>67</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>52</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>49</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>45</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>7328.8</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>5695.7</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>5680</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>5422</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>0.6486</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.629794</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.6846</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.6929999999999999</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>10.18</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.02</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>0.75</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -1366,51 +1456,57 @@
         <v>306</v>
       </c>
       <c r="D16" t="n">
+        <v>66</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="n">
         <v>177</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>142</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>187</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>200</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>20318.2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>16746.1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>21680.7</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>23230.5</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.0813</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.058247</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.08459999999999999</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.0833</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>51.07</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.08</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>9.59</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>9.94</v>
       </c>
     </row>
@@ -1427,51 +1523,57 @@
         <v>812</v>
       </c>
       <c r="D17" t="n">
+        <v>110</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="n">
         <v>381</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>298</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>407</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>395</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>46359.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>38360.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>49367.2</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>46725.9</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.0025</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.000269</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.0028</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.0029</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>72.75</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>41.23</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>32.43</v>
       </c>
     </row>
@@ -1488,51 +1590,57 @@
         <v>84</v>
       </c>
       <c r="D18" t="n">
+        <v>37</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
         <v>109</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>89</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>69</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>64</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>11279.9</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>9636.4</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>7389.7</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>7387.5</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.4451</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.410836</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.5211</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.519</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>10.37</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.03</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>1.77</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>1.73</v>
       </c>
     </row>
@@ -1549,51 +1657,57 @@
         <v>96</v>
       </c>
       <c r="D19" t="n">
+        <v>62</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="n">
         <v>133</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>122</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>73</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>73</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>14114.9</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>12554.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>8229.9</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>8229.9</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.3425</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.284721</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.4557</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.4557</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>8.52</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.05</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>2.65</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>2.62</v>
       </c>
     </row>
@@ -1610,51 +1724,57 @@
         <v>52</v>
       </c>
       <c r="D20" t="n">
+        <v>28</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
         <v>72</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>63</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>79</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>75</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>7918</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>6815.7</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>10111.7</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>9657.200000000001</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.5238</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.438898</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.5056</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.513</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>6.66</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.03</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>1.39</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -1690,6 +1810,8 @@
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1723,6 +1845,8 @@
       <c r="Q22" s="3" t="n"/>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1756,6 +1880,8 @@
       <c r="Q23" s="3" t="n"/>
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1789,10 +1915,12 @@
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
+      <c r="T24" s="3" t="n"/>
+      <c r="U24" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1804,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L157"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1819,6 +1947,8 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1846,45 +1976,55 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Num. Layers</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Max 2Q-Gates in Layer</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>ICCAD Steps</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>ZAC Steps</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>遗传zzx Steps(旧内核)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>ICCAD move μs</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>ZAC move μs</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>遗传zzx move(旧内核)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>ICCAD fid</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>ZAC fid</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>遗传zzx fid(旧内核)</t>
         </is>
@@ -1903,30 +2043,36 @@
         <v>102</v>
       </c>
       <c r="D3" t="n">
+        <v>70</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
         <v>145</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>163</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>88</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>14411.2</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>16381.2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>10051.3</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.288988</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.3191</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.4073</v>
       </c>
     </row>
@@ -1943,30 +2089,36 @@
         <v>17</v>
       </c>
       <c r="D4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>32</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>32</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>17</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>3015.8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>2970.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1612.5</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.8433</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.8462</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.8758</v>
       </c>
     </row>
@@ -1983,30 +2135,36 @@
         <v>97</v>
       </c>
       <c r="D5" t="n">
+        <v>89</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>179</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>181</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>95</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>16815.5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>17029.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>9465.9</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.358273</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.3715</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.4627</v>
       </c>
     </row>
@@ -2023,30 +2181,36 @@
         <v>66</v>
       </c>
       <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>121</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>122</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>66</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>11416.4</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>11490.4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>6696.7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.499625</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.5108</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.5904</v>
       </c>
     </row>
@@ -2063,30 +2227,36 @@
         <v>18</v>
       </c>
       <c r="D7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>28</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>24</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>15</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>2753.7</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>2391.4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1697.4</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.840849</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.86</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.8774999999999999</v>
       </c>
     </row>
@@ -2103,30 +2273,36 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>22</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>22</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>14</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>2205.8</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>2168.8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1591.2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.872406</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.8771</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.8946</v>
       </c>
     </row>
@@ -2143,30 +2319,36 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>16</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>1631.8</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>1592.9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>963.1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.906576</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.9095</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.9278</v>
       </c>
     </row>
@@ -2183,30 +2365,36 @@
         <v>116</v>
       </c>
       <c r="D10" t="n">
+        <v>98</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
         <v>195</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>192</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>107</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>18466.5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>18237.4</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>10917.2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.296933</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.3172</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.4031</v>
       </c>
     </row>
@@ -2223,30 +2411,36 @@
         <v>112</v>
       </c>
       <c r="D11" t="n">
+        <v>94</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
         <v>189</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>190</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>106</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>17883.5</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>18032.2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>10760.9</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.308178</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.3221</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.4093</v>
       </c>
     </row>
@@ -2263,30 +2457,36 @@
         <v>86</v>
       </c>
       <c r="D12" t="n">
+        <v>77</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
         <v>156</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>157</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>87</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>14891.2</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>14891.8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>8664.9</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.402844</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.417</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.501</v>
       </c>
     </row>
@@ -2303,30 +2503,36 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
+        <v>88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
         <v>181</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>189</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>101</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>18102.2</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>19278.3</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>11059.8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.339729</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.3531</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.4442</v>
       </c>
     </row>
@@ -2343,30 +2549,36 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
+        <v>27</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
         <v>55</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>54</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>31</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>5288.2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>5147.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>3078.6</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.728485</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.7365</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.7854</v>
       </c>
     </row>
@@ -2383,30 +2595,36 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
         <v>93</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>88</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>51</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>8838.799999999999</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>8850.799999999999</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>5079.2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.582523</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.611</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>0.6778999999999999</v>
       </c>
     </row>
@@ -2423,30 +2641,36 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
         <v>87</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>88</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>49</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>8288.6</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>8845.9</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>4835.8</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.603867</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.6224</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.6883</v>
       </c>
     </row>
@@ -2463,30 +2687,36 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
+        <v>26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
         <v>55</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>56</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>32</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>5330.7</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>5370.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>3189.2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.720093</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.7302999999999999</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.7838000000000001</v>
       </c>
     </row>
@@ -2503,30 +2733,36 @@
         <v>113</v>
       </c>
       <c r="D18" t="n">
+        <v>95</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
         <v>193</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>199</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>105</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>18307.3</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>19371.8</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>10565.3</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.30206</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.3158</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.4038</v>
       </c>
     </row>
@@ -2543,30 +2779,36 @@
         <v>179</v>
       </c>
       <c r="D19" t="n">
+        <v>160</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
         <v>316</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>315</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>178</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>29807.8</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>29689.9</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>17871.9</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.150638</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.1618</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.2382</v>
       </c>
     </row>
@@ -2583,30 +2825,36 @@
         <v>107</v>
       </c>
       <c r="D20" t="n">
+        <v>97</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
         <v>191</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>193</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>109</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>18131.9</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>18349.3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>11072.9</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.32353</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.3376</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.4231</v>
       </c>
     </row>
@@ -2623,30 +2871,36 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
+        <v>92</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
         <v>183</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>186</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
         <v>105</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>17323.4</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>17647.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>10648.7</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.334921</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.3489</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>0.4359</v>
       </c>
     </row>
@@ -2663,30 +2917,36 @@
         <v>79</v>
       </c>
       <c r="D22" t="n">
+        <v>71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
         <v>146</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>147</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>83</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>13975.6</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>14024.7</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>8496.4</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.430016</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.4436</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.5273</v>
       </c>
     </row>
@@ -2703,30 +2963,36 @@
         <v>119</v>
       </c>
       <c r="D23" t="n">
+        <v>108</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
         <v>222</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>222</v>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>121</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>20993.5</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>21796.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>12037.8</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.278165</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.2919</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>0.3844</v>
       </c>
     </row>
@@ -2743,30 +3009,36 @@
         <v>38</v>
       </c>
       <c r="D24" t="n">
+        <v>33</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
         <v>68</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>68</v>
       </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
         <v>38</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>6839</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>6475.9</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>4095.8</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.665071</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.6747</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.7347</v>
       </c>
     </row>
@@ -2783,30 +3055,36 @@
         <v>46</v>
       </c>
       <c r="D25" t="n">
+        <v>42</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
         <v>77</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>77</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
         <v>45</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>7336.7</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>7308.3</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>4490.8</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.624802</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.6348</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.6937</v>
       </c>
     </row>
@@ -2823,30 +3101,36 @@
         <v>58</v>
       </c>
       <c r="D26" t="n">
+        <v>51</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
         <v>105</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>105</v>
       </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
         <v>59</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>10049</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>9966.1</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>5981.6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.542866</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.5538</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.6259</v>
       </c>
     </row>
@@ -2863,30 +3147,36 @@
         <v>31</v>
       </c>
       <c r="D27" t="n">
+        <v>31</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
         <v>60</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>61</v>
       </c>
-      <c r="F27" t="n">
+      <c r="H27" t="n">
         <v>35</v>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>5942.1</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>6041.7</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>3910.1</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.714944</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.7251</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.7711</v>
       </c>
     </row>
@@ -2903,30 +3193,36 @@
         <v>31</v>
       </c>
       <c r="D28" t="n">
+        <v>31</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
         <v>56</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>56</v>
       </c>
-      <c r="F28" t="n">
+      <c r="H28" t="n">
         <v>31</v>
       </c>
-      <c r="G28" t="n">
+      <c r="I28" t="n">
         <v>5326.9</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>5286.9</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>3166.7</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.729549</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.7377</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0.7822</v>
       </c>
     </row>
@@ -2943,30 +3239,36 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
         <v>32</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>32</v>
       </c>
-      <c r="F29" t="n">
+      <c r="H29" t="n">
         <v>19</v>
       </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
         <v>3136.7</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>3096.6</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>2048.6</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.8422809999999999</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.8471</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -2983,30 +3285,36 @@
         <v>10</v>
       </c>
       <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
         <v>17</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>18</v>
       </c>
-      <c r="F30" t="n">
+      <c r="H30" t="n">
         <v>11</v>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>1728.9</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>2131</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>1164.2</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.897397</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.8998</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.9189000000000001</v>
       </c>
     </row>
@@ -3023,30 +3331,36 @@
         <v>11</v>
       </c>
       <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
         <v>19</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>20</v>
       </c>
-      <c r="F31" t="n">
+      <c r="H31" t="n">
         <v>12</v>
       </c>
-      <c r="G31" t="n">
+      <c r="I31" t="n">
         <v>1914.7</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>2007.6</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>1254.5</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.888827</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.8915999999999999</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>0.9117</v>
       </c>
     </row>
@@ -3063,30 +3377,36 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
         <v>61</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>61</v>
       </c>
-      <c r="F32" t="n">
+      <c r="H32" t="n">
         <v>34</v>
       </c>
-      <c r="G32" t="n">
+      <c r="I32" t="n">
         <v>5808.3</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>5761.7</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>3545.8</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.7089530000000001</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.7164</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.7689</v>
       </c>
     </row>
@@ -3103,30 +3423,36 @@
         <v>16</v>
       </c>
       <c r="D33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
         <v>31</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>32</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>18</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>3039.4</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>3105.7</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>1818.8</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.839224</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.844</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.8749</v>
       </c>
     </row>
@@ -3143,30 +3469,36 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
+        <v>66</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
         <v>127</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>129</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>69</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>12042</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>12184.6</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>7006.8</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.473684</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.4908</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -3183,30 +3515,36 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
+        <v>62</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
         <v>126</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>134</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>72</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>11938.4</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>15118.4</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>7116.5</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.477573</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.4859</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -3223,40 +3561,48 @@
         <v>15232</v>
       </c>
       <c r="D36" t="n">
+        <v>12849</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>27216</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>2677490.6</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3275,30 +3621,36 @@
         <v>205</v>
       </c>
       <c r="D37" t="n">
+        <v>173</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
         <v>355</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>364</v>
       </c>
-      <c r="F37" t="n">
+      <c r="H37" t="n">
         <v>203</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>33696.8</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>34773.6</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>21172.1</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.106911</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.1184</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.1873</v>
       </c>
     </row>
@@ -3315,32 +3667,38 @@
         <v>1498</v>
       </c>
       <c r="D38" t="n">
+        <v>1249</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
         <v>2607</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>2620</v>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="n">
         <v>1459</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>254470.9</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>256718.8</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>158198.6</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3355,30 +3713,36 @@
         <v>69</v>
       </c>
       <c r="D39" t="n">
+        <v>63</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
         <v>127</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>131</v>
       </c>
-      <c r="F39" t="n">
+      <c r="H39" t="n">
         <v>71</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>11998.8</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>12797.8</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>7032.1</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.484118</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.4965</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.5757</v>
       </c>
     </row>
@@ -3395,30 +3759,36 @@
         <v>38</v>
       </c>
       <c r="D40" t="n">
+        <v>35</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
         <v>70</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>72</v>
       </c>
-      <c r="F40" t="n">
+      <c r="H40" t="n">
         <v>40</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>6752.6</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>7005.2</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>4200.2</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.655594</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.6667999999999999</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.7299</v>
       </c>
     </row>
@@ -3435,30 +3805,36 @@
         <v>38</v>
       </c>
       <c r="D41" t="n">
+        <v>35</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
         <v>72</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>73</v>
       </c>
-      <c r="F41" t="n">
+      <c r="H41" t="n">
         <v>40</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>6882.3</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>6929.9</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>3895.3</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.6682</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>0.6765</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>0.7354000000000001</v>
       </c>
     </row>
@@ -3475,30 +3851,36 @@
         <v>17</v>
       </c>
       <c r="D42" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
         <v>30</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>32</v>
       </c>
-      <c r="F42" t="n">
+      <c r="H42" t="n">
         <v>18</v>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>2867.9</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>3061.5</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>1872.1</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.828186</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.8328</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.8648</v>
       </c>
     </row>
@@ -3515,30 +3897,36 @@
         <v>18</v>
       </c>
       <c r="D43" t="n">
+        <v>16</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
         <v>30</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
         <v>32</v>
       </c>
-      <c r="F43" t="n">
+      <c r="H43" t="n">
         <v>18</v>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>2869.3</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>3068.6</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>2118.4</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>0.823317</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>0.8279</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>0.8624000000000001</v>
       </c>
     </row>
@@ -3555,30 +3943,36 @@
         <v>17</v>
       </c>
       <c r="D44" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
         <v>30</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>32</v>
       </c>
-      <c r="F44" t="n">
+      <c r="H44" t="n">
         <v>18</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I44" t="n">
         <v>2864.5</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>3063.3</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>2106.2</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>0.828195</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>0.8328</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>0.8675</v>
       </c>
     </row>
@@ -3595,30 +3989,36 @@
         <v>223</v>
       </c>
       <c r="D45" t="n">
+        <v>199</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
         <v>397</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
         <v>397</v>
       </c>
-      <c r="F45" t="n">
+      <c r="H45" t="n">
         <v>221</v>
       </c>
-      <c r="G45" t="n">
+      <c r="I45" t="n">
         <v>37377.1</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>37475.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>22504.7</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0.092594</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>0.1023</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>0.1688</v>
       </c>
     </row>
@@ -3635,30 +4035,36 @@
         <v>198</v>
       </c>
       <c r="D46" t="n">
+        <v>172</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
         <v>347</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>351</v>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>196</v>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>32485.8</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>32904</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>19265.8</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>0.123786</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>0.1324</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>0.2057</v>
       </c>
     </row>
@@ -3675,30 +4081,36 @@
         <v>72</v>
       </c>
       <c r="D47" t="n">
+        <v>64</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
         <v>129</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>136</v>
       </c>
-      <c r="F47" t="n">
+      <c r="H47" t="n">
         <v>73</v>
       </c>
-      <c r="G47" t="n">
+      <c r="I47" t="n">
         <v>12160.1</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>12889.6</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>7205.2</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0.46421</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>0.4765</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>0.5569</v>
       </c>
     </row>
@@ -3715,30 +4127,36 @@
         <v>17</v>
       </c>
       <c r="D48" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
         <v>30</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
         <v>34</v>
       </c>
-      <c r="F48" t="n">
+      <c r="H48" t="n">
         <v>18</v>
       </c>
-      <c r="G48" t="n">
+      <c r="I48" t="n">
         <v>2867</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>3628.8</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>1872.1</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>0.828552</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>0.8312</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>0.8648</v>
       </c>
     </row>
@@ -3755,30 +4173,36 @@
         <v>24</v>
       </c>
       <c r="D49" t="n">
+        <v>23</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
         <v>46</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>46</v>
       </c>
-      <c r="F49" t="n">
+      <c r="H49" t="n">
         <v>27</v>
       </c>
-      <c r="G49" t="n">
+      <c r="I49" t="n">
         <v>4380</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>4337.6</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>2695.3</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0.771801</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>0.7786999999999999</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>0.8212</v>
       </c>
     </row>
@@ -3795,30 +4219,36 @@
         <v>18</v>
       </c>
       <c r="D50" t="n">
+        <v>16</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
         <v>32</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
         <v>34</v>
       </c>
-      <c r="F50" t="n">
+      <c r="H50" t="n">
         <v>19</v>
       </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
         <v>3043.1</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>3242.8</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>1962.4</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.819945</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>0.8249</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>0.8585</v>
       </c>
     </row>
@@ -3835,30 +4265,36 @@
         <v>49</v>
       </c>
       <c r="D51" t="n">
+        <v>44</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
         <v>90</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>92</v>
       </c>
-      <c r="F51" t="n">
+      <c r="H51" t="n">
         <v>49</v>
       </c>
-      <c r="G51" t="n">
+      <c r="I51" t="n">
         <v>8436.6</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>8642.200000000001</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>4933.9</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>0.5914700000000001</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>0.6009</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>0.6731</v>
       </c>
     </row>
@@ -3875,30 +4311,36 @@
         <v>18</v>
       </c>
       <c r="D52" t="n">
+        <v>16</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
         <v>32</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>34</v>
       </c>
-      <c r="F52" t="n">
+      <c r="H52" t="n">
         <v>19</v>
       </c>
-      <c r="G52" t="n">
+      <c r="I52" t="n">
         <v>3049.2</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>3242.8</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>1962.4</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>0.819928</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>0.8249</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>0.8585</v>
       </c>
     </row>
@@ -3915,40 +4357,48 @@
         <v>14772</v>
       </c>
       <c r="D53" t="n">
+        <v>12028</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>25940</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
         <v>2582779.9</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
         <v>0</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3967,30 +4417,36 @@
         <v>532</v>
       </c>
       <c r="D54" t="n">
+        <v>461</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
         <v>957</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>952</v>
       </c>
-      <c r="F54" t="n">
+      <c r="H54" t="n">
         <v>522</v>
       </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
         <v>93793.39999999999</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>91454.10000000001</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>51287.7</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.001778</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>0.0028</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>0.0112</v>
       </c>
     </row>
@@ -4007,30 +4463,36 @@
         <v>771</v>
       </c>
       <c r="D55" t="n">
+        <v>634</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="n">
         <v>1380</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>1311</v>
       </c>
-      <c r="F55" t="n">
+      <c r="H55" t="n">
         <v>738</v>
       </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
         <v>147782.3</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>126664.6</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>80058.39999999999</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>6.9e-05</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>0.0002</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>0.0013</v>
       </c>
     </row>
@@ -4047,30 +4509,36 @@
         <v>283</v>
       </c>
       <c r="D56" t="n">
+        <v>234</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
         <v>481</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>496</v>
       </c>
-      <c r="F56" t="n">
+      <c r="H56" t="n">
         <v>269</v>
       </c>
-      <c r="G56" t="n">
+      <c r="I56" t="n">
         <v>47056</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>48436.3</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>26568.7</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>0.043971</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>0.051</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -4087,34 +4555,42 @@
         <v>4986</v>
       </c>
       <c r="D57" t="n">
+        <v>4256</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>9025</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
         <v>8980</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
         <v>895813</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>881709</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4133,30 +4609,36 @@
         <v>75</v>
       </c>
       <c r="D58" t="n">
+        <v>41</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
         <v>92</v>
       </c>
-      <c r="E58" t="n">
+      <c r="G58" t="n">
         <v>117</v>
       </c>
-      <c r="F58" t="n">
+      <c r="H58" t="n">
         <v>64</v>
       </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
         <v>9140</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>11810.5</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>7414.7</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>0.385233</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>0.4154</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>0.5023</v>
       </c>
     </row>
@@ -4173,30 +4655,36 @@
         <v>205</v>
       </c>
       <c r="D59" t="n">
+        <v>144</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="n">
         <v>298</v>
       </c>
-      <c r="E59" t="n">
+      <c r="G59" t="n">
         <v>315</v>
       </c>
-      <c r="F59" t="n">
+      <c r="H59" t="n">
         <v>184</v>
       </c>
-      <c r="G59" t="n">
+      <c r="I59" t="n">
         <v>29566.3</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>30626.2</v>
       </c>
-      <c r="I59" t="n">
+      <c r="K59" t="n">
         <v>20656.1</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>0.07942399999999999</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>0.0989</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>0.1607</v>
       </c>
     </row>
@@ -4213,34 +4701,42 @@
         <v>7840</v>
       </c>
       <c r="D60" t="n">
+        <v>5759</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>13707</v>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
         <v>13432</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
         <v>1411821.1</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>1361303.7</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
         <v>0</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4259,30 +4755,36 @@
         <v>415</v>
       </c>
       <c r="D61" t="n">
+        <v>346</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="n">
         <v>733</v>
       </c>
-      <c r="E61" t="n">
+      <c r="G61" t="n">
         <v>716</v>
       </c>
-      <c r="F61" t="n">
+      <c r="H61" t="n">
         <v>411</v>
       </c>
-      <c r="G61" t="n">
+      <c r="I61" t="n">
         <v>72715.7</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>69296.39999999999</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>41714.1</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>0.009312000000000001</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>0.0123</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>0.0323</v>
       </c>
     </row>
@@ -4299,32 +4801,38 @@
         <v>2644</v>
       </c>
       <c r="D62" t="n">
+        <v>2271</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="n">
         <v>4733</v>
       </c>
-      <c r="E62" t="n">
+      <c r="G62" t="n">
         <v>4737</v>
       </c>
-      <c r="F62" t="n">
+      <c r="H62" t="n">
         <v>2584</v>
       </c>
-      <c r="G62" t="n">
+      <c r="I62" t="n">
         <v>459243</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>459184.8</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>269679.5</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4339,30 +4847,36 @@
         <v>833</v>
       </c>
       <c r="D63" t="n">
+        <v>705</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" t="n">
         <v>1444</v>
       </c>
-      <c r="E63" t="n">
+      <c r="G63" t="n">
         <v>1431</v>
       </c>
-      <c r="F63" t="n">
+      <c r="H63" t="n">
         <v>779</v>
       </c>
-      <c r="G63" t="n">
+      <c r="I63" t="n">
         <v>140293</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>137135.7</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>83517</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>6.499999999999999e-05</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>0.0001</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -4379,34 +4893,42 @@
         <v>4131</v>
       </c>
       <c r="D64" t="n">
+        <v>3518</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>7429</v>
       </c>
-      <c r="E64" t="n">
+      <c r="G64" t="n">
         <v>7434</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
         <v>729274.5</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>728197.3</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
         <v>0</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
         <v>0</v>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4425,40 +4947,48 @@
         <v>16624</v>
       </c>
       <c r="D65" t="n">
+        <v>13274</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
         <v>29164</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
         <v>2919694.9</v>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
         <v>0</v>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4477,30 +5007,36 @@
         <v>9</v>
       </c>
       <c r="D66" t="n">
+        <v>9</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
         <v>18</v>
       </c>
-      <c r="E66" t="n">
+      <c r="G66" t="n">
         <v>18</v>
       </c>
-      <c r="F66" t="n">
+      <c r="H66" t="n">
         <v>10</v>
       </c>
-      <c r="G66" t="n">
+      <c r="I66" t="n">
         <v>1736.5</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>1701.5</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>979.7</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>0.9095</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>0.9117</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>0.9295</v>
       </c>
     </row>
@@ -4517,30 +5053,36 @@
         <v>5</v>
       </c>
       <c r="D67" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
         <v>10</v>
       </c>
-      <c r="E67" t="n">
+      <c r="G67" t="n">
         <v>10</v>
       </c>
-      <c r="F67" t="n">
+      <c r="H67" t="n">
         <v>9</v>
       </c>
-      <c r="G67" t="n">
+      <c r="I67" t="n">
         <v>1146</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>1131.4</v>
       </c>
-      <c r="I67" t="n">
+      <c r="K67" t="n">
         <v>1108.4</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>0.944392</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
         <v>0.947</v>
       </c>
-      <c r="L67" t="n">
+      <c r="N67" t="n">
         <v>0.9509</v>
       </c>
     </row>
@@ -4557,30 +5099,36 @@
         <v>275</v>
       </c>
       <c r="D68" t="n">
+        <v>241</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="n">
         <v>490</v>
       </c>
-      <c r="E68" t="n">
+      <c r="G68" t="n">
         <v>489</v>
       </c>
-      <c r="F68" t="n">
+      <c r="H68" t="n">
         <v>279</v>
       </c>
-      <c r="G68" t="n">
+      <c r="I68" t="n">
         <v>46356.1</v>
       </c>
-      <c r="H68" t="n">
+      <c r="J68" t="n">
         <v>46819.2</v>
       </c>
-      <c r="I68" t="n">
+      <c r="K68" t="n">
         <v>28828.6</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>0.049321</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
         <v>0.0562</v>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>0.1069</v>
       </c>
     </row>
@@ -4597,30 +5145,36 @@
         <v>175</v>
       </c>
       <c r="D69" t="n">
+        <v>157</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="n">
         <v>315</v>
       </c>
-      <c r="E69" t="n">
+      <c r="G69" t="n">
         <v>320</v>
       </c>
-      <c r="F69" t="n">
+      <c r="H69" t="n">
         <v>169</v>
       </c>
-      <c r="G69" t="n">
+      <c r="I69" t="n">
         <v>29692</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>30225.3</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>16998.8</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>0.155133</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
         <v>0.1666</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>0.2477</v>
       </c>
     </row>
@@ -4637,30 +5191,36 @@
         <v>525</v>
       </c>
       <c r="D70" t="n">
+        <v>449</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="n">
         <v>916</v>
       </c>
-      <c r="E70" t="n">
+      <c r="G70" t="n">
         <v>924</v>
       </c>
-      <c r="F70" t="n">
+      <c r="H70" t="n">
         <v>510</v>
       </c>
-      <c r="G70" t="n">
+      <c r="I70" t="n">
         <v>87232.3</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>89046.39999999999</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>52333.2</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>0.003063</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
         <v>0.0041</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>0.0136</v>
       </c>
     </row>
@@ -4677,30 +5237,36 @@
         <v>5</v>
       </c>
       <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
         <v>10</v>
       </c>
-      <c r="E71" t="n">
+      <c r="G71" t="n">
         <v>10</v>
       </c>
-      <c r="F71" t="n">
+      <c r="H71" t="n">
         <v>9</v>
       </c>
-      <c r="G71" t="n">
+      <c r="I71" t="n">
         <v>1128.1</v>
       </c>
-      <c r="H71" t="n">
+      <c r="J71" t="n">
         <v>1123</v>
       </c>
-      <c r="I71" t="n">
+      <c r="K71" t="n">
         <v>1109.6</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>0.943566</v>
       </c>
-      <c r="K71" t="n">
+      <c r="M71" t="n">
         <v>0.9455</v>
       </c>
-      <c r="L71" t="n">
+      <c r="N71" t="n">
         <v>0.9494</v>
       </c>
     </row>
@@ -4717,30 +5283,36 @@
         <v>154209</v>
       </c>
       <c r="D72" t="n">
+        <v>151095</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
         <v>255476</v>
       </c>
-      <c r="E72" t="n">
+      <c r="G72" t="n">
         <v>2</v>
       </c>
-      <c r="F72" t="n">
+      <c r="H72" t="n">
         <v>1</v>
       </c>
-      <c r="G72" t="n">
+      <c r="I72" t="n">
         <v>24513023.8</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>200</v>
       </c>
-      <c r="I72" t="n">
+      <c r="K72" t="n">
         <v>109.1</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>0</v>
       </c>
-      <c r="K72" t="n">
+      <c r="M72" t="n">
         <v>0.9722</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>0.9768</v>
       </c>
     </row>
@@ -4757,34 +5329,42 @@
         <v>3856</v>
       </c>
       <c r="D73" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
         <v>6774</v>
       </c>
-      <c r="E73" t="n">
+      <c r="G73" t="n">
         <v>6804</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
         <v>660671.3</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>664500.2</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
         <v>0</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4803,30 +5383,36 @@
         <v>9</v>
       </c>
       <c r="D74" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
         <v>18</v>
       </c>
-      <c r="E74" t="n">
+      <c r="G74" t="n">
         <v>18</v>
       </c>
-      <c r="F74" t="n">
+      <c r="H74" t="n">
         <v>10</v>
       </c>
-      <c r="G74" t="n">
+      <c r="I74" t="n">
         <v>1741.3</v>
       </c>
-      <c r="H74" t="n">
+      <c r="J74" t="n">
         <v>1705</v>
       </c>
-      <c r="I74" t="n">
+      <c r="K74" t="n">
         <v>980.8</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>0.909828</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
         <v>0.9122</v>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -4843,30 +5429,36 @@
         <v>149</v>
       </c>
       <c r="D75" t="n">
+        <v>134</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
         <v>264</v>
       </c>
-      <c r="E75" t="n">
+      <c r="G75" t="n">
         <v>266</v>
       </c>
-      <c r="F75" t="n">
+      <c r="H75" t="n">
         <v>149</v>
       </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
         <v>25027.6</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>25771</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>15307.5</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>0.201402</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
         <v>0.2151</v>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
         <v>0.3007</v>
       </c>
     </row>
@@ -4883,30 +5475,36 @@
         <v>105</v>
       </c>
       <c r="D76" t="n">
+        <v>97</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
         <v>191</v>
       </c>
-      <c r="E76" t="n">
+      <c r="G76" t="n">
         <v>192</v>
       </c>
-      <c r="F76" t="n">
+      <c r="H76" t="n">
         <v>106</v>
       </c>
-      <c r="G76" t="n">
+      <c r="I76" t="n">
         <v>18489.6</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>18090.9</v>
       </c>
-      <c r="I76" t="n">
+      <c r="K76" t="n">
         <v>10167.3</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>0.334788</v>
       </c>
-      <c r="K76" t="n">
+      <c r="M76" t="n">
         <v>0.3491</v>
       </c>
-      <c r="L76" t="n">
+      <c r="N76" t="n">
         <v>0.4397</v>
       </c>
     </row>
@@ -4923,30 +5521,36 @@
         <v>598</v>
       </c>
       <c r="D77" t="n">
+        <v>535</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="n">
         <v>1081</v>
       </c>
-      <c r="E77" t="n">
+      <c r="G77" t="n">
         <v>1091</v>
       </c>
-      <c r="F77" t="n">
+      <c r="H77" t="n">
         <v>588</v>
       </c>
-      <c r="G77" t="n">
+      <c r="I77" t="n">
         <v>102033.2</v>
       </c>
-      <c r="H77" t="n">
+      <c r="J77" t="n">
         <v>103084.3</v>
       </c>
-      <c r="I77" t="n">
+      <c r="K77" t="n">
         <v>58960.1</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>0.001646</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
         <v>0.0021</v>
       </c>
-      <c r="L77" t="n">
+      <c r="N77" t="n">
         <v>0.008399999999999999</v>
       </c>
     </row>
@@ -4963,32 +5567,38 @@
         <v>2952</v>
       </c>
       <c r="D78" t="n">
+        <v>2559</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
         <v>5265</v>
       </c>
-      <c r="E78" t="n">
+      <c r="G78" t="n">
         <v>5225</v>
       </c>
-      <c r="F78" t="n">
+      <c r="H78" t="n">
         <v>2867</v>
       </c>
-      <c r="G78" t="n">
+      <c r="I78" t="n">
         <v>506663.1</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>493872.2</v>
       </c>
-      <c r="I78" t="n">
+      <c r="K78" t="n">
         <v>292231.3</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5003,34 +5613,42 @@
         <v>10677</v>
       </c>
       <c r="D79" t="n">
+        <v>9108</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
         <v>18710</v>
       </c>
-      <c r="E79" t="n">
+      <c r="G79" t="n">
         <v>18716</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
         <v>1792577</v>
       </c>
-      <c r="H79" t="n">
+      <c r="J79" t="n">
         <v>1786361.7</v>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
         <v>0</v>
       </c>
-      <c r="K79" t="n">
+      <c r="M79" t="n">
         <v>-0</v>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5049,40 +5667,48 @@
         <v>30368</v>
       </c>
       <c r="D80" t="n">
+        <v>26038</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
         <v>53805</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
         <v>5193560.2</v>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
         <v>0</v>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5101,40 +5727,48 @@
         <v>90949</v>
       </c>
       <c r="D81" t="n">
+        <v>77959</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
         <v>162422</v>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
         <v>15815893.1</v>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
         <v>0</v>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5153,34 +5787,42 @@
         <v>4636</v>
       </c>
       <c r="D82" t="n">
+        <v>3928</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
         <v>8239</v>
       </c>
-      <c r="E82" t="n">
+      <c r="G82" t="n">
         <v>8202</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
         <v>807559</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>796259.4</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
         <v>0</v>
       </c>
-      <c r="K82" t="n">
+      <c r="M82" t="n">
         <v>0</v>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5199,30 +5841,36 @@
         <v>90</v>
       </c>
       <c r="D83" t="n">
+        <v>20</v>
+      </c>
+      <c r="E83" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" t="n">
         <v>36</v>
       </c>
-      <c r="E83" t="n">
+      <c r="G83" t="n">
         <v>46</v>
       </c>
-      <c r="F83" t="n">
+      <c r="H83" t="n">
         <v>24</v>
       </c>
-      <c r="G83" t="n">
+      <c r="I83" t="n">
         <v>4250.7</v>
       </c>
-      <c r="H83" t="n">
+      <c r="J83" t="n">
         <v>5552.2</v>
       </c>
-      <c r="I83" t="n">
+      <c r="K83" t="n">
         <v>3066.1</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>0.457297</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
         <v>0.4765</v>
       </c>
-      <c r="L83" t="n">
+      <c r="N83" t="n">
         <v>0.5101</v>
       </c>
     </row>
@@ -5239,30 +5887,36 @@
         <v>120</v>
       </c>
       <c r="D84" t="n">
+        <v>20</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="n">
         <v>40</v>
       </c>
-      <c r="E84" t="n">
+      <c r="G84" t="n">
         <v>66</v>
       </c>
-      <c r="F84" t="n">
+      <c r="H84" t="n">
         <v>42</v>
       </c>
-      <c r="G84" t="n">
+      <c r="I84" t="n">
         <v>4914.7</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>7793.3</v>
       </c>
-      <c r="I84" t="n">
+      <c r="K84" t="n">
         <v>5788.4</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>0.345018</v>
       </c>
-      <c r="K84" t="n">
+      <c r="M84" t="n">
         <v>0.3742</v>
       </c>
-      <c r="L84" t="n">
+      <c r="N84" t="n">
         <v>0.3962</v>
       </c>
     </row>
@@ -5279,30 +5933,36 @@
         <v>150</v>
       </c>
       <c r="D85" t="n">
+        <v>20</v>
+      </c>
+      <c r="E85" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" t="n">
         <v>35</v>
       </c>
-      <c r="E85" t="n">
+      <c r="G85" t="n">
         <v>66</v>
       </c>
-      <c r="F85" t="n">
+      <c r="H85" t="n">
         <v>42</v>
       </c>
-      <c r="G85" t="n">
+      <c r="I85" t="n">
         <v>4331</v>
       </c>
-      <c r="H85" t="n">
+      <c r="J85" t="n">
         <v>7799.3</v>
       </c>
-      <c r="I85" t="n">
+      <c r="K85" t="n">
         <v>6577.7</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>0.261506</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
         <v>0.2878</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>0.3101</v>
       </c>
     </row>
@@ -5319,34 +5979,42 @@
         <v>9800</v>
       </c>
       <c r="D86" t="n">
+        <v>8356</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
         <v>17469</v>
       </c>
-      <c r="E86" t="n">
+      <c r="G86" t="n">
         <v>17508</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
         <v>1704799.3</v>
       </c>
-      <c r="H86" t="n">
+      <c r="J86" t="n">
         <v>1700662.4</v>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
         <v>0</v>
       </c>
-      <c r="K86" t="n">
+      <c r="M86" t="n">
         <v>-0</v>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5365,30 +6033,36 @@
         <v>267</v>
       </c>
       <c r="D87" t="n">
+        <v>232</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" t="n">
         <v>474</v>
       </c>
-      <c r="E87" t="n">
+      <c r="G87" t="n">
         <v>479</v>
       </c>
-      <c r="F87" t="n">
+      <c r="H87" t="n">
         <v>262</v>
       </c>
-      <c r="G87" t="n">
+      <c r="I87" t="n">
         <v>45066.3</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>46729.9</v>
       </c>
-      <c r="I87" t="n">
+      <c r="K87" t="n">
         <v>26981.6</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>0.054629</v>
       </c>
-      <c r="K87" t="n">
+      <c r="M87" t="n">
         <v>0.0614</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>0.115</v>
       </c>
     </row>
@@ -5405,34 +6079,42 @@
         <v>11844</v>
       </c>
       <c r="D88" t="n">
+        <v>9657</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
         <v>20602</v>
       </c>
-      <c r="E88" t="n">
+      <c r="G88" t="n">
         <v>20511</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
         <v>2024549.2</v>
       </c>
-      <c r="H88" t="n">
+      <c r="J88" t="n">
         <v>1998553.6</v>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
         <v>0</v>
       </c>
-      <c r="K88" t="n">
+      <c r="M88" t="n">
         <v>0</v>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5451,30 +6133,36 @@
         <v>23</v>
       </c>
       <c r="D89" t="n">
+        <v>23</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
         <v>46</v>
       </c>
-      <c r="E89" t="n">
+      <c r="G89" t="n">
         <v>46</v>
       </c>
-      <c r="F89" t="n">
+      <c r="H89" t="n">
         <v>24</v>
       </c>
-      <c r="G89" t="n">
+      <c r="I89" t="n">
         <v>4293.3</v>
       </c>
-      <c r="H89" t="n">
+      <c r="J89" t="n">
         <v>4250.5</v>
       </c>
-      <c r="I89" t="n">
+      <c r="K89" t="n">
         <v>2247.4</v>
       </c>
-      <c r="J89" t="n">
+      <c r="L89" t="n">
         <v>0.790673</v>
       </c>
-      <c r="K89" t="n">
+      <c r="M89" t="n">
         <v>0.7947</v>
       </c>
-      <c r="L89" t="n">
+      <c r="N89" t="n">
         <v>0.8351</v>
       </c>
     </row>
@@ -5491,30 +6179,36 @@
         <v>126</v>
       </c>
       <c r="D90" t="n">
+        <v>111</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
         <v>225</v>
       </c>
-      <c r="E90" t="n">
+      <c r="G90" t="n">
         <v>239</v>
       </c>
-      <c r="F90" t="n">
+      <c r="H90" t="n">
         <v>131</v>
       </c>
-      <c r="G90" t="n">
+      <c r="I90" t="n">
         <v>21678.7</v>
       </c>
-      <c r="H90" t="n">
+      <c r="J90" t="n">
         <v>24050.9</v>
       </c>
-      <c r="I90" t="n">
+      <c r="K90" t="n">
         <v>12721.3</v>
       </c>
-      <c r="J90" t="n">
+      <c r="L90" t="n">
         <v>0.26178</v>
       </c>
-      <c r="K90" t="n">
+      <c r="M90" t="n">
         <v>0.2741</v>
       </c>
-      <c r="L90" t="n">
+      <c r="N90" t="n">
         <v>0.3633</v>
       </c>
     </row>
@@ -5531,30 +6225,36 @@
         <v>77</v>
       </c>
       <c r="D91" t="n">
+        <v>53</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="n">
         <v>113</v>
       </c>
-      <c r="E91" t="n">
+      <c r="G91" t="n">
         <v>125</v>
       </c>
-      <c r="F91" t="n">
+      <c r="H91" t="n">
         <v>81</v>
       </c>
-      <c r="G91" t="n">
+      <c r="I91" t="n">
         <v>11400.9</v>
       </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
         <v>12568.6</v>
       </c>
-      <c r="I91" t="n">
+      <c r="K91" t="n">
         <v>9092.299999999999</v>
       </c>
-      <c r="J91" t="n">
+      <c r="L91" t="n">
         <v>0.419851</v>
       </c>
-      <c r="K91" t="n">
+      <c r="M91" t="n">
         <v>0.4399</v>
       </c>
-      <c r="L91" t="n">
+      <c r="N91" t="n">
         <v>0.5133</v>
       </c>
     </row>
@@ -5571,32 +6271,38 @@
         <v>2100</v>
       </c>
       <c r="D92" t="n">
+        <v>1797</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3</v>
+      </c>
+      <c r="F92" t="n">
         <v>3751</v>
       </c>
-      <c r="E92" t="n">
+      <c r="G92" t="n">
         <v>3723</v>
       </c>
-      <c r="F92" t="n">
+      <c r="H92" t="n">
         <v>2031</v>
       </c>
-      <c r="G92" t="n">
+      <c r="I92" t="n">
         <v>367914.2</v>
       </c>
-      <c r="H92" t="n">
+      <c r="J92" t="n">
         <v>361883.5</v>
       </c>
-      <c r="I92" t="n">
+      <c r="K92" t="n">
         <v>216316.5</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5611,34 +6317,42 @@
         <v>8232</v>
       </c>
       <c r="D93" t="n">
+        <v>6930</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
         <v>14780</v>
       </c>
-      <c r="E93" t="n">
+      <c r="G93" t="n">
         <v>14706</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
         <v>1455396.2</v>
       </c>
-      <c r="H93" t="n">
+      <c r="J93" t="n">
         <v>1439865.5</v>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
         <v>0</v>
       </c>
-      <c r="K93" t="n">
+      <c r="M93" t="n">
         <v>0</v>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5657,30 +6371,36 @@
         <v>108</v>
       </c>
       <c r="D94" t="n">
+        <v>97</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="n">
         <v>195</v>
       </c>
-      <c r="E94" t="n">
+      <c r="G94" t="n">
         <v>196</v>
       </c>
-      <c r="F94" t="n">
+      <c r="H94" t="n">
         <v>106</v>
       </c>
-      <c r="G94" t="n">
+      <c r="I94" t="n">
         <v>18958.2</v>
       </c>
-      <c r="H94" t="n">
+      <c r="J94" t="n">
         <v>18985.7</v>
       </c>
-      <c r="I94" t="n">
+      <c r="K94" t="n">
         <v>10593.4</v>
       </c>
-      <c r="J94" t="n">
+      <c r="L94" t="n">
         <v>0.321531</v>
       </c>
-      <c r="K94" t="n">
+      <c r="M94" t="n">
         <v>0.3347</v>
       </c>
-      <c r="L94" t="n">
+      <c r="N94" t="n">
         <v>0.4247</v>
       </c>
     </row>
@@ -5697,30 +6417,36 @@
         <v>78</v>
       </c>
       <c r="D95" t="n">
+        <v>70</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="n">
         <v>137</v>
       </c>
-      <c r="E95" t="n">
+      <c r="G95" t="n">
         <v>141</v>
       </c>
-      <c r="F95" t="n">
+      <c r="H95" t="n">
         <v>75</v>
       </c>
-      <c r="G95" t="n">
+      <c r="I95" t="n">
         <v>13008.4</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>13407.1</v>
       </c>
-      <c r="I95" t="n">
+      <c r="K95" t="n">
         <v>7773</v>
       </c>
-      <c r="J95" t="n">
+      <c r="L95" t="n">
         <v>0.439776</v>
       </c>
-      <c r="K95" t="n">
+      <c r="M95" t="n">
         <v>0.451</v>
       </c>
-      <c r="L95" t="n">
+      <c r="N95" t="n">
         <v>0.5364</v>
       </c>
     </row>
@@ -5737,30 +6463,36 @@
         <v>239</v>
       </c>
       <c r="D96" t="n">
+        <v>208</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
         <v>419</v>
       </c>
-      <c r="E96" t="n">
+      <c r="G96" t="n">
         <v>431</v>
       </c>
-      <c r="F96" t="n">
+      <c r="H96" t="n">
         <v>229</v>
       </c>
-      <c r="G96" t="n">
+      <c r="I96" t="n">
         <v>39369</v>
       </c>
-      <c r="H96" t="n">
+      <c r="J96" t="n">
         <v>41227.4</v>
       </c>
-      <c r="I96" t="n">
+      <c r="K96" t="n">
         <v>24751.4</v>
       </c>
-      <c r="J96" t="n">
+      <c r="L96" t="n">
         <v>0.07799</v>
       </c>
-      <c r="K96" t="n">
+      <c r="M96" t="n">
         <v>0.0858</v>
       </c>
-      <c r="L96" t="n">
+      <c r="N96" t="n">
         <v>0.146</v>
       </c>
     </row>
@@ -5777,30 +6509,36 @@
         <v>13</v>
       </c>
       <c r="D97" t="n">
+        <v>11</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="n">
         <v>24</v>
       </c>
-      <c r="E97" t="n">
+      <c r="G97" t="n">
         <v>26</v>
       </c>
-      <c r="F97" t="n">
+      <c r="H97" t="n">
         <v>14</v>
       </c>
-      <c r="G97" t="n">
+      <c r="I97" t="n">
         <v>2382.1</v>
       </c>
-      <c r="H97" t="n">
+      <c r="J97" t="n">
         <v>3005.8</v>
       </c>
-      <c r="I97" t="n">
+      <c r="K97" t="n">
         <v>1448.2</v>
       </c>
-      <c r="J97" t="n">
+      <c r="L97" t="n">
         <v>0.8632570000000001</v>
       </c>
-      <c r="K97" t="n">
+      <c r="M97" t="n">
         <v>0.8657</v>
       </c>
-      <c r="L97" t="n">
+      <c r="N97" t="n">
         <v>0.8965</v>
       </c>
     </row>
@@ -5817,30 +6555,36 @@
         <v>25</v>
       </c>
       <c r="D98" t="n">
+        <v>25</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
         <v>50</v>
       </c>
-      <c r="E98" t="n">
+      <c r="G98" t="n">
         <v>50</v>
       </c>
-      <c r="F98" t="n">
+      <c r="H98" t="n">
         <v>28</v>
       </c>
-      <c r="G98" t="n">
+      <c r="I98" t="n">
         <v>4765.3</v>
       </c>
-      <c r="H98" t="n">
+      <c r="J98" t="n">
         <v>4730</v>
       </c>
-      <c r="I98" t="n">
+      <c r="K98" t="n">
         <v>2970.4</v>
       </c>
-      <c r="J98" t="n">
+      <c r="L98" t="n">
         <v>0.767288</v>
       </c>
-      <c r="K98" t="n">
+      <c r="M98" t="n">
         <v>0.7742</v>
       </c>
-      <c r="L98" t="n">
+      <c r="N98" t="n">
         <v>0.8151</v>
       </c>
     </row>
@@ -5857,30 +6601,36 @@
         <v>16</v>
       </c>
       <c r="D99" t="n">
+        <v>16</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="n">
         <v>32</v>
       </c>
-      <c r="E99" t="n">
+      <c r="G99" t="n">
         <v>32</v>
       </c>
-      <c r="F99" t="n">
+      <c r="H99" t="n">
         <v>19</v>
       </c>
-      <c r="G99" t="n">
+      <c r="I99" t="n">
         <v>3141.4</v>
       </c>
-      <c r="H99" t="n">
+      <c r="J99" t="n">
         <v>3101.5</v>
       </c>
-      <c r="I99" t="n">
+      <c r="K99" t="n">
         <v>2023.6</v>
       </c>
-      <c r="J99" t="n">
+      <c r="L99" t="n">
         <v>0.842638</v>
       </c>
-      <c r="K99" t="n">
+      <c r="M99" t="n">
         <v>0.8471</v>
       </c>
-      <c r="L99" t="n">
+      <c r="N99" t="n">
         <v>0.8741</v>
       </c>
     </row>
@@ -5897,30 +6647,36 @@
         <v>196</v>
       </c>
       <c r="D100" t="n">
+        <v>178</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
         <v>355</v>
       </c>
-      <c r="E100" t="n">
+      <c r="G100" t="n">
         <v>354</v>
       </c>
-      <c r="F100" t="n">
+      <c r="H100" t="n">
         <v>195</v>
       </c>
-      <c r="G100" t="n">
+      <c r="I100" t="n">
         <v>33494.4</v>
       </c>
-      <c r="H100" t="n">
+      <c r="J100" t="n">
         <v>34228</v>
       </c>
-      <c r="I100" t="n">
+      <c r="K100" t="n">
         <v>19407.2</v>
       </c>
-      <c r="J100" t="n">
+      <c r="L100" t="n">
         <v>0.124327</v>
       </c>
-      <c r="K100" t="n">
+      <c r="M100" t="n">
         <v>0.1372</v>
       </c>
-      <c r="L100" t="n">
+      <c r="N100" t="n">
         <v>0.2137</v>
       </c>
     </row>
@@ -5937,30 +6693,36 @@
         <v>152</v>
       </c>
       <c r="D101" t="n">
+        <v>135</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" t="n">
         <v>275</v>
       </c>
-      <c r="E101" t="n">
+      <c r="G101" t="n">
         <v>280</v>
       </c>
-      <c r="F101" t="n">
+      <c r="H101" t="n">
         <v>152</v>
       </c>
-      <c r="G101" t="n">
+      <c r="I101" t="n">
         <v>25999.6</v>
       </c>
-      <c r="H101" t="n">
+      <c r="J101" t="n">
         <v>26559</v>
       </c>
-      <c r="I101" t="n">
+      <c r="K101" t="n">
         <v>15719.7</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>0.196076</v>
       </c>
-      <c r="K101" t="n">
+      <c r="M101" t="n">
         <v>0.2087</v>
       </c>
-      <c r="L101" t="n">
+      <c r="N101" t="n">
         <v>0.2947</v>
       </c>
     </row>
@@ -5977,30 +6739,36 @@
         <v>128</v>
       </c>
       <c r="D102" t="n">
+        <v>116</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" t="n">
         <v>236</v>
       </c>
-      <c r="E102" t="n">
+      <c r="G102" t="n">
         <v>237</v>
       </c>
-      <c r="F102" t="n">
+      <c r="H102" t="n">
         <v>127</v>
       </c>
-      <c r="G102" t="n">
+      <c r="I102" t="n">
         <v>22215.8</v>
       </c>
-      <c r="H102" t="n">
+      <c r="J102" t="n">
         <v>22329.2</v>
       </c>
-      <c r="I102" t="n">
+      <c r="K102" t="n">
         <v>12853.9</v>
       </c>
-      <c r="J102" t="n">
+      <c r="L102" t="n">
         <v>0.258466</v>
       </c>
-      <c r="K102" t="n">
+      <c r="M102" t="n">
         <v>0.2695</v>
       </c>
-      <c r="L102" t="n">
+      <c r="N102" t="n">
         <v>0.3586</v>
       </c>
     </row>
@@ -6017,30 +6785,36 @@
         <v>65</v>
       </c>
       <c r="D103" t="n">
+        <v>59</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" t="n">
         <v>116</v>
       </c>
-      <c r="E103" t="n">
+      <c r="G103" t="n">
         <v>119</v>
       </c>
-      <c r="F103" t="n">
+      <c r="H103" t="n">
         <v>64</v>
       </c>
-      <c r="G103" t="n">
+      <c r="I103" t="n">
         <v>10968.6</v>
       </c>
-      <c r="H103" t="n">
+      <c r="J103" t="n">
         <v>11744.2</v>
       </c>
-      <c r="I103" t="n">
+      <c r="K103" t="n">
         <v>6239.6</v>
       </c>
-      <c r="J103" t="n">
+      <c r="L103" t="n">
         <v>0.505557</v>
       </c>
-      <c r="K103" t="n">
+      <c r="M103" t="n">
         <v>0.5174</v>
       </c>
-      <c r="L103" t="n">
+      <c r="N103" t="n">
         <v>0.5983000000000001</v>
       </c>
     </row>
@@ -6057,30 +6831,36 @@
         <v>59</v>
       </c>
       <c r="D104" t="n">
+        <v>56</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" t="n">
         <v>113</v>
       </c>
-      <c r="E104" t="n">
+      <c r="G104" t="n">
         <v>115</v>
       </c>
-      <c r="F104" t="n">
+      <c r="H104" t="n">
         <v>61</v>
       </c>
-      <c r="G104" t="n">
+      <c r="I104" t="n">
         <v>10569.5</v>
       </c>
-      <c r="H104" t="n">
+      <c r="J104" t="n">
         <v>10771.4</v>
       </c>
-      <c r="I104" t="n">
+      <c r="K104" t="n">
         <v>6040</v>
       </c>
-      <c r="J104" t="n">
+      <c r="L104" t="n">
         <v>0.536835</v>
       </c>
-      <c r="K104" t="n">
+      <c r="M104" t="n">
         <v>0.5474</v>
       </c>
-      <c r="L104" t="n">
+      <c r="N104" t="n">
         <v>0.6251</v>
       </c>
     </row>
@@ -6097,30 +6877,36 @@
         <v>32</v>
       </c>
       <c r="D105" t="n">
+        <v>29</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="n">
         <v>59</v>
       </c>
-      <c r="E105" t="n">
+      <c r="G105" t="n">
         <v>62</v>
       </c>
-      <c r="F105" t="n">
+      <c r="H105" t="n">
         <v>32</v>
       </c>
-      <c r="G105" t="n">
+      <c r="I105" t="n">
         <v>5681.6</v>
       </c>
-      <c r="H105" t="n">
+      <c r="J105" t="n">
         <v>6547.6</v>
       </c>
-      <c r="I105" t="n">
+      <c r="K105" t="n">
         <v>3375.9</v>
       </c>
-      <c r="J105" t="n">
+      <c r="L105" t="n">
         <v>0.7083199999999999</v>
       </c>
-      <c r="K105" t="n">
+      <c r="M105" t="n">
         <v>0.7145</v>
       </c>
-      <c r="L105" t="n">
+      <c r="N105" t="n">
         <v>0.7709</v>
       </c>
     </row>
@@ -6137,30 +6923,36 @@
         <v>32</v>
       </c>
       <c r="D106" t="n">
+        <v>29</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" t="n">
         <v>60</v>
       </c>
-      <c r="E106" t="n">
+      <c r="G106" t="n">
         <v>64</v>
       </c>
-      <c r="F106" t="n">
+      <c r="H106" t="n">
         <v>34</v>
       </c>
-      <c r="G106" t="n">
+      <c r="I106" t="n">
         <v>5750.8</v>
       </c>
-      <c r="H106" t="n">
+      <c r="J106" t="n">
         <v>7357</v>
       </c>
-      <c r="I106" t="n">
+      <c r="K106" t="n">
         <v>3584</v>
       </c>
-      <c r="J106" t="n">
+      <c r="L106" t="n">
         <v>0.705356</v>
       </c>
-      <c r="K106" t="n">
+      <c r="M106" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L106" t="n">
+      <c r="N106" t="n">
         <v>0.7689</v>
       </c>
     </row>
@@ -6177,40 +6969,48 @@
         <v>56317</v>
       </c>
       <c r="D107" t="n">
+        <v>48259</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>101817</v>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
         <v>9982906</v>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
         <v>0</v>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6229,40 +7029,48 @@
         <v>81853</v>
       </c>
       <c r="D108" t="n">
+        <v>70214</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>148487</v>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
         <v>14605054.5</v>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
         <v>0</v>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6281,30 +7089,36 @@
         <v>771</v>
       </c>
       <c r="D109" t="n">
+        <v>634</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="n">
         <v>1380</v>
       </c>
-      <c r="E109" t="n">
+      <c r="G109" t="n">
         <v>1311</v>
       </c>
-      <c r="F109" t="n">
+      <c r="H109" t="n">
         <v>738</v>
       </c>
-      <c r="G109" t="n">
+      <c r="I109" t="n">
         <v>147782.3</v>
       </c>
-      <c r="H109" t="n">
+      <c r="J109" t="n">
         <v>126664.6</v>
       </c>
-      <c r="I109" t="n">
+      <c r="K109" t="n">
         <v>80058.39999999999</v>
       </c>
-      <c r="J109" t="n">
+      <c r="L109" t="n">
         <v>6.9e-05</v>
       </c>
-      <c r="K109" t="n">
+      <c r="M109" t="n">
         <v>0.0002</v>
       </c>
-      <c r="L109" t="n">
+      <c r="N109" t="n">
         <v>0.0013</v>
       </c>
     </row>
@@ -6321,30 +7135,36 @@
         <v>27</v>
       </c>
       <c r="D110" t="n">
+        <v>19</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="n">
         <v>15</v>
       </c>
-      <c r="E110" t="n">
+      <c r="G110" t="n">
         <v>20</v>
       </c>
-      <c r="F110" t="n">
+      <c r="H110" t="n">
         <v>12</v>
       </c>
-      <c r="G110" t="n">
+      <c r="I110" t="n">
         <v>1524.7</v>
       </c>
-      <c r="H110" t="n">
+      <c r="J110" t="n">
         <v>2205.8</v>
       </c>
-      <c r="I110" t="n">
+      <c r="K110" t="n">
         <v>1328.3</v>
       </c>
-      <c r="J110" t="n">
+      <c r="L110" t="n">
         <v>0.804601</v>
       </c>
-      <c r="K110" t="n">
+      <c r="M110" t="n">
         <v>0.8193</v>
       </c>
-      <c r="L110" t="n">
+      <c r="N110" t="n">
         <v>0.8414</v>
       </c>
     </row>
@@ -6361,30 +7181,36 @@
         <v>38</v>
       </c>
       <c r="D111" t="n">
+        <v>26</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="n">
         <v>18</v>
       </c>
-      <c r="E111" t="n">
+      <c r="G111" t="n">
         <v>20</v>
       </c>
-      <c r="F111" t="n">
+      <c r="H111" t="n">
         <v>13</v>
       </c>
-      <c r="G111" t="n">
+      <c r="I111" t="n">
         <v>1945.1</v>
       </c>
-      <c r="H111" t="n">
+      <c r="J111" t="n">
         <v>2184.4</v>
       </c>
-      <c r="I111" t="n">
+      <c r="K111" t="n">
         <v>1502.3</v>
       </c>
-      <c r="J111" t="n">
+      <c r="L111" t="n">
         <v>0.756046</v>
       </c>
-      <c r="K111" t="n">
+      <c r="M111" t="n">
         <v>0.8197</v>
       </c>
-      <c r="L111" t="n">
+      <c r="N111" t="n">
         <v>0.8331</v>
       </c>
     </row>
@@ -6401,40 +7227,48 @@
         <v>90</v>
       </c>
       <c r="D112" t="n">
+        <v>34</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
         <v>56</v>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
         <v>6161.6</v>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
         <v>0.44087</v>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6453,40 +7287,48 @@
         <v>240</v>
       </c>
       <c r="D113" t="n">
+        <v>58</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
         <v>106</v>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
         <v>12226</v>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
         <v>0.1019</v>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6505,32 +7347,38 @@
         <v>1405</v>
       </c>
       <c r="D114" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="n">
         <v>2504</v>
       </c>
-      <c r="E114" t="n">
+      <c r="G114" t="n">
         <v>2511</v>
       </c>
-      <c r="F114" t="n">
+      <c r="H114" t="n">
         <v>1372</v>
       </c>
-      <c r="G114" t="n">
+      <c r="I114" t="n">
         <v>244126.6</v>
       </c>
-      <c r="H114" t="n">
+      <c r="J114" t="n">
         <v>244530</v>
       </c>
-      <c r="I114" t="n">
+      <c r="K114" t="n">
         <v>142234.6</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6545,30 +7393,36 @@
         <v>12</v>
       </c>
       <c r="D115" t="n">
+        <v>12</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
         <v>24</v>
       </c>
-      <c r="E115" t="n">
+      <c r="G115" t="n">
         <v>24</v>
       </c>
-      <c r="F115" t="n">
+      <c r="H115" t="n">
         <v>14</v>
       </c>
-      <c r="G115" t="n">
+      <c r="I115" t="n">
         <v>2335.9</v>
       </c>
-      <c r="H115" t="n">
+      <c r="J115" t="n">
         <v>2295.8</v>
       </c>
-      <c r="I115" t="n">
+      <c r="K115" t="n">
         <v>1495.8</v>
       </c>
-      <c r="J115" t="n">
+      <c r="L115" t="n">
         <v>0.879852</v>
       </c>
-      <c r="K115" t="n">
+      <c r="M115" t="n">
         <v>0.8837</v>
       </c>
-      <c r="L115" t="n">
+      <c r="N115" t="n">
         <v>0.9051</v>
       </c>
     </row>
@@ -6585,30 +7439,36 @@
         <v>12</v>
       </c>
       <c r="D116" t="n">
+        <v>12</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="n">
         <v>24</v>
       </c>
-      <c r="E116" t="n">
+      <c r="G116" t="n">
         <v>24</v>
       </c>
-      <c r="F116" t="n">
+      <c r="H116" t="n">
         <v>14</v>
       </c>
-      <c r="G116" t="n">
+      <c r="I116" t="n">
         <v>2335.9</v>
       </c>
-      <c r="H116" t="n">
+      <c r="J116" t="n">
         <v>2295.8</v>
       </c>
-      <c r="I116" t="n">
+      <c r="K116" t="n">
         <v>1495.8</v>
       </c>
-      <c r="J116" t="n">
+      <c r="L116" t="n">
         <v>0.879852</v>
       </c>
-      <c r="K116" t="n">
+      <c r="M116" t="n">
         <v>0.8834</v>
       </c>
-      <c r="L116" t="n">
+      <c r="N116" t="n">
         <v>0.9048</v>
       </c>
     </row>
@@ -6625,30 +7485,36 @@
         <v>36</v>
       </c>
       <c r="D117" t="n">
+        <v>35</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" t="n">
         <v>68</v>
       </c>
-      <c r="E117" t="n">
+      <c r="G117" t="n">
         <v>68</v>
       </c>
-      <c r="F117" t="n">
+      <c r="H117" t="n">
         <v>37</v>
       </c>
-      <c r="G117" t="n">
+      <c r="I117" t="n">
         <v>6444</v>
       </c>
-      <c r="H117" t="n">
+      <c r="J117" t="n">
         <v>6411.4</v>
       </c>
-      <c r="I117" t="n">
+      <c r="K117" t="n">
         <v>3667.3</v>
       </c>
-      <c r="J117" t="n">
+      <c r="L117" t="n">
         <v>0.684307</v>
       </c>
-      <c r="K117" t="n">
+      <c r="M117" t="n">
         <v>0.6929</v>
       </c>
-      <c r="L117" t="n">
+      <c r="N117" t="n">
         <v>0.7495000000000001</v>
       </c>
     </row>
@@ -6665,30 +7531,36 @@
         <v>448</v>
       </c>
       <c r="D118" t="n">
+        <v>383</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" t="n">
         <v>792</v>
       </c>
-      <c r="E118" t="n">
+      <c r="G118" t="n">
         <v>785</v>
       </c>
-      <c r="F118" t="n">
+      <c r="H118" t="n">
         <v>438</v>
       </c>
-      <c r="G118" t="n">
+      <c r="I118" t="n">
         <v>76843.2</v>
       </c>
-      <c r="H118" t="n">
+      <c r="J118" t="n">
         <v>74298.60000000001</v>
       </c>
-      <c r="I118" t="n">
+      <c r="K118" t="n">
         <v>45977.4</v>
       </c>
-      <c r="J118" t="n">
+      <c r="L118" t="n">
         <v>0.007358</v>
       </c>
-      <c r="K118" t="n">
+      <c r="M118" t="n">
         <v>0.0092</v>
       </c>
-      <c r="L118" t="n">
+      <c r="N118" t="n">
         <v>0.0257</v>
       </c>
     </row>
@@ -6705,30 +7577,36 @@
         <v>198</v>
       </c>
       <c r="D119" t="n">
+        <v>173</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" t="n">
         <v>360</v>
       </c>
-      <c r="E119" t="n">
+      <c r="G119" t="n">
         <v>357</v>
       </c>
-      <c r="F119" t="n">
+      <c r="H119" t="n">
         <v>195</v>
       </c>
-      <c r="G119" t="n">
+      <c r="I119" t="n">
         <v>34341.3</v>
       </c>
-      <c r="H119" t="n">
+      <c r="J119" t="n">
         <v>34934.4</v>
       </c>
-      <c r="I119" t="n">
+      <c r="K119" t="n">
         <v>20089.3</v>
       </c>
-      <c r="J119" t="n">
+      <c r="L119" t="n">
         <v>0.11374</v>
       </c>
-      <c r="K119" t="n">
+      <c r="M119" t="n">
         <v>0.1244</v>
       </c>
-      <c r="L119" t="n">
+      <c r="N119" t="n">
         <v>0.1969</v>
       </c>
     </row>
@@ -6745,30 +7623,36 @@
         <v>252</v>
       </c>
       <c r="D120" t="n">
+        <v>219</v>
+      </c>
+      <c r="E120" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" t="n">
         <v>443</v>
       </c>
-      <c r="E120" t="n">
+      <c r="G120" t="n">
         <v>447</v>
       </c>
-      <c r="F120" t="n">
+      <c r="H120" t="n">
         <v>242</v>
       </c>
-      <c r="G120" t="n">
+      <c r="I120" t="n">
         <v>41954.3</v>
       </c>
-      <c r="H120" t="n">
+      <c r="J120" t="n">
         <v>42336.8</v>
       </c>
-      <c r="I120" t="n">
+      <c r="K120" t="n">
         <v>24484.3</v>
       </c>
-      <c r="J120" t="n">
+      <c r="L120" t="n">
         <v>0.064635</v>
       </c>
-      <c r="K120" t="n">
+      <c r="M120" t="n">
         <v>0.0726</v>
       </c>
-      <c r="L120" t="n">
+      <c r="N120" t="n">
         <v>0.1295</v>
       </c>
     </row>
@@ -6785,30 +7669,36 @@
         <v>134</v>
       </c>
       <c r="D121" t="n">
+        <v>114</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" t="n">
         <v>228</v>
       </c>
-      <c r="E121" t="n">
+      <c r="G121" t="n">
         <v>229</v>
       </c>
-      <c r="F121" t="n">
+      <c r="H121" t="n">
         <v>128</v>
       </c>
-      <c r="G121" t="n">
+      <c r="I121" t="n">
         <v>21793.1</v>
       </c>
-      <c r="H121" t="n">
+      <c r="J121" t="n">
         <v>21870.6</v>
       </c>
-      <c r="I121" t="n">
+      <c r="K121" t="n">
         <v>13031.3</v>
       </c>
-      <c r="J121" t="n">
+      <c r="L121" t="n">
         <v>0.235767</v>
       </c>
-      <c r="K121" t="n">
+      <c r="M121" t="n">
         <v>0.2507</v>
       </c>
-      <c r="L121" t="n">
+      <c r="N121" t="n">
         <v>0.3382</v>
       </c>
     </row>
@@ -6825,30 +7715,36 @@
         <v>60</v>
       </c>
       <c r="D122" t="n">
+        <v>42</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2</v>
+      </c>
+      <c r="F122" t="n">
         <v>87</v>
       </c>
-      <c r="E122" t="n">
+      <c r="G122" t="n">
         <v>99</v>
       </c>
-      <c r="F122" t="n">
+      <c r="H122" t="n">
         <v>51</v>
       </c>
-      <c r="G122" t="n">
+      <c r="I122" t="n">
         <v>9281.6</v>
       </c>
-      <c r="H122" t="n">
+      <c r="J122" t="n">
         <v>10032.1</v>
       </c>
-      <c r="I122" t="n">
+      <c r="K122" t="n">
         <v>5854.2</v>
       </c>
-      <c r="J122" t="n">
+      <c r="L122" t="n">
         <v>0.521632</v>
       </c>
-      <c r="K122" t="n">
+      <c r="M122" t="n">
         <v>0.5366</v>
       </c>
-      <c r="L122" t="n">
+      <c r="N122" t="n">
         <v>0.6035</v>
       </c>
     </row>
@@ -6865,30 +7761,36 @@
         <v>564</v>
       </c>
       <c r="D123" t="n">
+        <v>492</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" t="n">
         <v>1025</v>
       </c>
-      <c r="E123" t="n">
+      <c r="G123" t="n">
         <v>996</v>
       </c>
-      <c r="F123" t="n">
+      <c r="H123" t="n">
         <v>563</v>
       </c>
-      <c r="G123" t="n">
+      <c r="I123" t="n">
         <v>100259.8</v>
       </c>
-      <c r="H123" t="n">
+      <c r="J123" t="n">
         <v>94542.39999999999</v>
       </c>
-      <c r="I123" t="n">
+      <c r="K123" t="n">
         <v>57957.3</v>
       </c>
-      <c r="J123" t="n">
+      <c r="L123" t="n">
         <v>0.001906</v>
       </c>
-      <c r="K123" t="n">
+      <c r="M123" t="n">
         <v>0.0027</v>
       </c>
-      <c r="L123" t="n">
+      <c r="N123" t="n">
         <v>0.009900000000000001</v>
       </c>
     </row>
@@ -6905,30 +7807,36 @@
         <v>124</v>
       </c>
       <c r="D124" t="n">
+        <v>92</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" t="n">
         <v>196</v>
       </c>
-      <c r="E124" t="n">
+      <c r="G124" t="n">
         <v>203</v>
       </c>
-      <c r="F124" t="n">
+      <c r="H124" t="n">
         <v>117</v>
       </c>
-      <c r="G124" t="n">
+      <c r="I124" t="n">
         <v>19077</v>
       </c>
-      <c r="H124" t="n">
+      <c r="J124" t="n">
         <v>19548.7</v>
       </c>
-      <c r="I124" t="n">
+      <c r="K124" t="n">
         <v>13175.2</v>
       </c>
-      <c r="J124" t="n">
+      <c r="L124" t="n">
         <v>0.22832</v>
       </c>
-      <c r="K124" t="n">
+      <c r="M124" t="n">
         <v>0.2546</v>
       </c>
-      <c r="L124" t="n">
+      <c r="N124" t="n">
         <v>0.3395</v>
       </c>
     </row>
@@ -6945,30 +7853,36 @@
         <v>104</v>
       </c>
       <c r="D125" t="n">
+        <v>68</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" t="n">
         <v>148</v>
       </c>
-      <c r="E125" t="n">
+      <c r="G125" t="n">
         <v>157</v>
       </c>
-      <c r="F125" t="n">
+      <c r="H125" t="n">
         <v>92</v>
       </c>
-      <c r="G125" t="n">
+      <c r="I125" t="n">
         <v>16035</v>
       </c>
-      <c r="H125" t="n">
+      <c r="J125" t="n">
         <v>15665.9</v>
       </c>
-      <c r="I125" t="n">
+      <c r="K125" t="n">
         <v>10045.4</v>
       </c>
-      <c r="J125" t="n">
+      <c r="L125" t="n">
         <v>0.312764</v>
       </c>
-      <c r="K125" t="n">
+      <c r="M125" t="n">
         <v>0.3359</v>
       </c>
-      <c r="L125" t="n">
+      <c r="N125" t="n">
         <v>0.4154</v>
       </c>
     </row>
@@ -6985,32 +7899,38 @@
         <v>2319</v>
       </c>
       <c r="D126" t="n">
+        <v>1963</v>
+      </c>
+      <c r="E126" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" t="n">
         <v>4007</v>
       </c>
-      <c r="E126" t="n">
+      <c r="G126" t="n">
         <v>4053</v>
       </c>
-      <c r="F126" t="n">
+      <c r="H126" t="n">
         <v>2244</v>
       </c>
-      <c r="G126" t="n">
+      <c r="I126" t="n">
         <v>385517.2</v>
       </c>
-      <c r="H126" t="n">
+      <c r="J126" t="n">
         <v>391160.1</v>
       </c>
-      <c r="I126" t="n">
+      <c r="K126" t="n">
         <v>230860</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7025,30 +7945,36 @@
         <v>154</v>
       </c>
       <c r="D127" t="n">
+        <v>81</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" t="n">
         <v>180</v>
       </c>
-      <c r="E127" t="n">
+      <c r="G127" t="n">
         <v>259</v>
       </c>
-      <c r="F127" t="n">
+      <c r="H127" t="n">
         <v>122</v>
       </c>
-      <c r="G127" t="n">
+      <c r="I127" t="n">
         <v>19660.8</v>
       </c>
-      <c r="H127" t="n">
+      <c r="J127" t="n">
         <v>27978.2</v>
       </c>
-      <c r="I127" t="n">
+      <c r="K127" t="n">
         <v>14334.1</v>
       </c>
-      <c r="J127" t="n">
+      <c r="L127" t="n">
         <v>0.16153</v>
       </c>
-      <c r="K127" t="n">
+      <c r="M127" t="n">
         <v>0.173</v>
       </c>
-      <c r="L127" t="n">
+      <c r="N127" t="n">
         <v>0.2561</v>
       </c>
     </row>
@@ -7065,34 +7991,42 @@
         <v>5960</v>
       </c>
       <c r="D128" t="n">
+        <v>4917</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
         <v>10438</v>
       </c>
-      <c r="E128" t="n">
+      <c r="G128" t="n">
         <v>10398</v>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
         <v>1027563</v>
       </c>
-      <c r="H128" t="n">
+      <c r="J128" t="n">
         <v>1012035.1</v>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" t="n">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
         <v>0</v>
       </c>
-      <c r="K128" t="n">
+      <c r="M128" t="n">
         <v>0</v>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="N128" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7111,34 +8045,42 @@
         <v>7493</v>
       </c>
       <c r="D129" t="n">
+        <v>5965</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>12927</v>
       </c>
-      <c r="E129" t="n">
+      <c r="G129" t="n">
         <v>12931</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
         <v>1285862.8</v>
       </c>
-      <c r="H129" t="n">
+      <c r="J129" t="n">
         <v>1277489.7</v>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" t="n">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
         <v>0</v>
       </c>
-      <c r="K129" t="n">
+      <c r="M129" t="n">
         <v>0</v>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="N129" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7157,40 +8099,48 @@
         <v>16864</v>
       </c>
       <c r="D130" t="n">
+        <v>13209</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
         <v>29330</v>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
         <v>2949953.6</v>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J130" t="n">
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
         <v>0</v>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7209,30 +8159,36 @@
         <v>336</v>
       </c>
       <c r="D131" t="n">
+        <v>300</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" t="n">
         <v>600</v>
       </c>
-      <c r="E131" t="n">
+      <c r="G131" t="n">
         <v>613</v>
       </c>
-      <c r="F131" t="n">
+      <c r="H131" t="n">
         <v>337</v>
       </c>
-      <c r="G131" t="n">
+      <c r="I131" t="n">
         <v>56105.2</v>
       </c>
-      <c r="H131" t="n">
+      <c r="J131" t="n">
         <v>57597.4</v>
       </c>
-      <c r="I131" t="n">
+      <c r="K131" t="n">
         <v>33866.1</v>
       </c>
-      <c r="J131" t="n">
+      <c r="L131" t="n">
         <v>0.028477</v>
       </c>
-      <c r="K131" t="n">
+      <c r="M131" t="n">
         <v>0.0324</v>
       </c>
-      <c r="L131" t="n">
+      <c r="N131" t="n">
         <v>0.0688</v>
       </c>
     </row>
@@ -7249,30 +8205,36 @@
         <v>336</v>
       </c>
       <c r="D132" t="n">
+        <v>301</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" t="n">
         <v>604</v>
       </c>
-      <c r="E132" t="n">
+      <c r="G132" t="n">
         <v>609</v>
       </c>
-      <c r="F132" t="n">
+      <c r="H132" t="n">
         <v>324</v>
       </c>
-      <c r="G132" t="n">
+      <c r="I132" t="n">
         <v>57400.5</v>
       </c>
-      <c r="H132" t="n">
+      <c r="J132" t="n">
         <v>57962.2</v>
       </c>
-      <c r="I132" t="n">
+      <c r="K132" t="n">
         <v>33820.3</v>
       </c>
-      <c r="J132" t="n">
+      <c r="L132" t="n">
         <v>0.02821</v>
       </c>
-      <c r="K132" t="n">
+      <c r="M132" t="n">
         <v>0.0322</v>
       </c>
-      <c r="L132" t="n">
+      <c r="N132" t="n">
         <v>0.06859999999999999</v>
       </c>
     </row>
@@ -7289,34 +8251,42 @@
         <v>4459</v>
       </c>
       <c r="D133" t="n">
+        <v>3719</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
         <v>7711</v>
       </c>
-      <c r="E133" t="n">
+      <c r="G133" t="n">
         <v>7662</v>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
         <v>744883.5</v>
       </c>
-      <c r="H133" t="n">
+      <c r="J133" t="n">
         <v>737083.6</v>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
         <v>0</v>
       </c>
-      <c r="K133" t="n">
+      <c r="M133" t="n">
         <v>0</v>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="N133" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7335,32 +8305,38 @@
         <v>1314</v>
       </c>
       <c r="D134" t="n">
+        <v>1121</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" t="n">
         <v>2318</v>
       </c>
-      <c r="E134" t="n">
+      <c r="G134" t="n">
         <v>2337</v>
       </c>
-      <c r="F134" t="n">
+      <c r="H134" t="n">
         <v>1287</v>
       </c>
-      <c r="G134" t="n">
+      <c r="I134" t="n">
         <v>224942.9</v>
       </c>
-      <c r="H134" t="n">
+      <c r="J134" t="n">
         <v>225864</v>
       </c>
-      <c r="I134" t="n">
+      <c r="K134" t="n">
         <v>134991.7</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
       </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7375,30 +8351,36 @@
         <v>869</v>
       </c>
       <c r="D135" t="n">
+        <v>720</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" t="n">
         <v>1478</v>
       </c>
-      <c r="E135" t="n">
+      <c r="G135" t="n">
         <v>1492</v>
       </c>
-      <c r="F135" t="n">
+      <c r="H135" t="n">
         <v>822</v>
       </c>
-      <c r="G135" t="n">
+      <c r="I135" t="n">
         <v>142957.7</v>
       </c>
-      <c r="H135" t="n">
+      <c r="J135" t="n">
         <v>144954.3</v>
       </c>
-      <c r="I135" t="n">
+      <c r="K135" t="n">
         <v>90585.8</v>
       </c>
-      <c r="J135" t="n">
+      <c r="L135" t="n">
         <v>3.1e-05</v>
       </c>
-      <c r="K135" t="n">
+      <c r="M135" t="n">
         <v>0.0001</v>
       </c>
-      <c r="L135" t="n">
+      <c r="N135" t="n">
         <v>0.0005999999999999999</v>
       </c>
     </row>
@@ -7415,32 +8397,38 @@
         <v>3089</v>
       </c>
       <c r="D136" t="n">
+        <v>2520</v>
+      </c>
+      <c r="E136" t="n">
+        <v>7</v>
+      </c>
+      <c r="F136" t="n">
         <v>5363</v>
       </c>
-      <c r="E136" t="n">
+      <c r="G136" t="n">
         <v>5427</v>
       </c>
-      <c r="F136" t="n">
+      <c r="H136" t="n">
         <v>2991</v>
       </c>
-      <c r="G136" t="n">
+      <c r="I136" t="n">
         <v>528004.6</v>
       </c>
-      <c r="H136" t="n">
+      <c r="J136" t="n">
         <v>533457.3</v>
       </c>
-      <c r="I136" t="n">
+      <c r="K136" t="n">
         <v>317906.5</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
       </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7455,40 +8443,48 @@
         <v>28084</v>
       </c>
       <c r="D137" t="n">
+        <v>23736</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
         <v>50402</v>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
         <v>4948495.6</v>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J137" t="n">
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
         <v>0</v>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7507,32 +8503,38 @@
         <v>1701</v>
       </c>
       <c r="D138" t="n">
+        <v>1499</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3</v>
+      </c>
+      <c r="F138" t="n">
         <v>3058</v>
       </c>
-      <c r="E138" t="n">
+      <c r="G138" t="n">
         <v>3056</v>
       </c>
-      <c r="F138" t="n">
+      <c r="H138" t="n">
         <v>1662</v>
       </c>
-      <c r="G138" t="n">
+      <c r="I138" t="n">
         <v>291414.8</v>
       </c>
-      <c r="H138" t="n">
+      <c r="J138" t="n">
         <v>289332</v>
       </c>
-      <c r="I138" t="n">
+      <c r="K138" t="n">
         <v>167464.2</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7547,30 +8549,36 @@
         <v>123</v>
       </c>
       <c r="D139" t="n">
+        <v>98</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" t="n">
         <v>206</v>
       </c>
-      <c r="E139" t="n">
+      <c r="G139" t="n">
         <v>215</v>
       </c>
-      <c r="F139" t="n">
+      <c r="H139" t="n">
         <v>120</v>
       </c>
-      <c r="G139" t="n">
+      <c r="I139" t="n">
         <v>20154</v>
       </c>
-      <c r="H139" t="n">
+      <c r="J139" t="n">
         <v>21000.8</v>
       </c>
-      <c r="I139" t="n">
+      <c r="K139" t="n">
         <v>13989.1</v>
       </c>
-      <c r="J139" t="n">
+      <c r="L139" t="n">
         <v>0.222884</v>
       </c>
-      <c r="K139" t="n">
+      <c r="M139" t="n">
         <v>0.2479</v>
       </c>
-      <c r="L139" t="n">
+      <c r="N139" t="n">
         <v>0.3321</v>
       </c>
     </row>
@@ -7587,30 +8595,36 @@
         <v>148</v>
       </c>
       <c r="D140" t="n">
+        <v>91</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2</v>
+      </c>
+      <c r="F140" t="n">
         <v>208</v>
       </c>
-      <c r="E140" t="n">
+      <c r="G140" t="n">
         <v>227</v>
       </c>
-      <c r="F140" t="n">
+      <c r="H140" t="n">
         <v>126</v>
       </c>
-      <c r="G140" t="n">
+      <c r="I140" t="n">
         <v>22996</v>
       </c>
-      <c r="H140" t="n">
+      <c r="J140" t="n">
         <v>23100.3</v>
       </c>
-      <c r="I140" t="n">
+      <c r="K140" t="n">
         <v>14684.6</v>
       </c>
-      <c r="J140" t="n">
+      <c r="L140" t="n">
         <v>0.18017</v>
       </c>
-      <c r="K140" t="n">
+      <c r="M140" t="n">
         <v>0.2024</v>
       </c>
-      <c r="L140" t="n">
+      <c r="N140" t="n">
         <v>0.2765</v>
       </c>
     </row>
@@ -7627,34 +8641,42 @@
         <v>9408</v>
       </c>
       <c r="D141" t="n">
+        <v>8062</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
         <v>16795</v>
       </c>
-      <c r="E141" t="n">
+      <c r="G141" t="n">
         <v>16643</v>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
         <v>1626794.1</v>
       </c>
-      <c r="H141" t="n">
+      <c r="J141" t="n">
         <v>1592960</v>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J141" t="n">
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
         <v>0</v>
       </c>
-      <c r="K141" t="n">
+      <c r="M141" t="n">
         <v>0</v>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="N141" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7673,40 +8695,48 @@
         <v>15232</v>
       </c>
       <c r="D142" t="n">
+        <v>12849</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
         <v>27216</v>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
         <v>2677490.6</v>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J142" t="n">
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
         <v>0</v>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7725,30 +8755,36 @@
         <v>98</v>
       </c>
       <c r="D143" t="n">
+        <v>55</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
         <v>120</v>
       </c>
-      <c r="E143" t="n">
+      <c r="G143" t="n">
         <v>158</v>
       </c>
-      <c r="F143" t="n">
+      <c r="H143" t="n">
         <v>76</v>
       </c>
-      <c r="G143" t="n">
+      <c r="I143" t="n">
         <v>12786.2</v>
       </c>
-      <c r="H143" t="n">
+      <c r="J143" t="n">
         <v>16278.3</v>
       </c>
-      <c r="I143" t="n">
+      <c r="K143" t="n">
         <v>9278.700000000001</v>
       </c>
-      <c r="J143" t="n">
+      <c r="L143" t="n">
         <v>0.338579</v>
       </c>
-      <c r="K143" t="n">
+      <c r="M143" t="n">
         <v>0.3529</v>
       </c>
-      <c r="L143" t="n">
+      <c r="N143" t="n">
         <v>0.4326</v>
       </c>
     </row>
@@ -7765,40 +8801,48 @@
         <v>80878</v>
       </c>
       <c r="D144" t="n">
+        <v>72933</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
         <v>141219</v>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
         <v>13584182.6</v>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J144" t="n">
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
         <v>0</v>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7817,40 +8861,48 @@
         <v>26676</v>
       </c>
       <c r="D145" t="n">
+        <v>22293</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
         <v>46734</v>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
         <v>4569699.9</v>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J145" t="n">
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
         <v>0</v>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7869,40 +8921,48 @@
         <v>35210</v>
       </c>
       <c r="D146" t="n">
+        <v>32247</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
         <v>63183</v>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
         <v>6204170.4</v>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J146" t="n">
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
         <v>0</v>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7921,34 +8981,42 @@
         <v>10062</v>
       </c>
       <c r="D147" t="n">
+        <v>8311</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
         <v>17467</v>
       </c>
-      <c r="E147" t="n">
+      <c r="G147" t="n">
         <v>17434</v>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G147" t="n">
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
         <v>1698398.2</v>
       </c>
-      <c r="H147" t="n">
+      <c r="J147" t="n">
         <v>1673658.5</v>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J147" t="n">
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
         <v>0</v>
       </c>
-      <c r="K147" t="n">
+      <c r="M147" t="n">
         <v>0</v>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="N147" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7967,40 +9035,48 @@
         <v>185276</v>
       </c>
       <c r="D148" t="n">
+        <v>167215</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
         <v>324890</v>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G148" t="n">
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
         <v>31434884.7</v>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J148" t="n">
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
         <v>0</v>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8019,40 +9095,48 @@
         <v>60346</v>
       </c>
       <c r="D149" t="n">
+        <v>50546</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
         <v>106240</v>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
         <v>10430041.8</v>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J149" t="n">
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
         <v>0</v>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8071,40 +9155,48 @@
         <v>224028</v>
       </c>
       <c r="D150" t="n">
+        <v>185975</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
         <v>374530</v>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
         <v>36279688.4</v>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J150" t="n">
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
         <v>0</v>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8123,40 +9215,48 @@
         <v>71932</v>
       </c>
       <c r="D151" t="n">
+        <v>64750</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
         <v>126624</v>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
         <v>12217797.9</v>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J151" t="n">
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
         <v>0</v>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8175,40 +9275,48 @@
         <v>23742</v>
       </c>
       <c r="D152" t="n">
+        <v>19880</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
         <v>41237</v>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
         <v>3993726.6</v>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J152" t="n">
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
         <v>0</v>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8227,40 +9335,48 @@
         <v>75180</v>
       </c>
       <c r="D153" t="n">
+        <v>67637</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
         <v>133060</v>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G153" t="n">
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
         <v>13030690.6</v>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J153" t="n">
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
         <v>0</v>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8279,30 +9395,36 @@
         <v>427</v>
       </c>
       <c r="D154" t="n">
+        <v>352</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3</v>
+      </c>
+      <c r="F154" t="n">
         <v>721</v>
       </c>
-      <c r="E154" t="n">
+      <c r="G154" t="n">
         <v>719</v>
       </c>
-      <c r="F154" t="n">
+      <c r="H154" t="n">
         <v>409</v>
       </c>
-      <c r="G154" t="n">
+      <c r="I154" t="n">
         <v>69158.10000000001</v>
       </c>
-      <c r="H154" t="n">
+      <c r="J154" t="n">
         <v>68749.10000000001</v>
       </c>
-      <c r="I154" t="n">
+      <c r="K154" t="n">
         <v>42991.9</v>
       </c>
-      <c r="J154" t="n">
+      <c r="L154" t="n">
         <v>0.007252</v>
       </c>
-      <c r="K154" t="n">
+      <c r="M154" t="n">
         <v>0.01</v>
       </c>
-      <c r="L154" t="n">
+      <c r="N154" t="n">
         <v>0.0278</v>
       </c>
     </row>
@@ -8319,30 +9441,36 @@
         <v>5</v>
       </c>
       <c r="D155" t="n">
+        <v>5</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
         <v>10</v>
       </c>
-      <c r="E155" t="n">
+      <c r="G155" t="n">
         <v>10</v>
       </c>
-      <c r="F155" t="n">
+      <c r="H155" t="n">
         <v>9</v>
       </c>
-      <c r="G155" t="n">
+      <c r="I155" t="n">
         <v>1146</v>
       </c>
-      <c r="H155" t="n">
+      <c r="J155" t="n">
         <v>1131.4</v>
       </c>
-      <c r="I155" t="n">
+      <c r="K155" t="n">
         <v>1108.4</v>
       </c>
-      <c r="J155" t="n">
+      <c r="L155" t="n">
         <v>0.944392</v>
       </c>
-      <c r="K155" t="n">
+      <c r="M155" t="n">
         <v>0.947</v>
       </c>
-      <c r="L155" t="n">
+      <c r="N155" t="n">
         <v>0.9509</v>
       </c>
     </row>
@@ -8359,32 +9487,38 @@
         <v>1343</v>
       </c>
       <c r="D156" t="n">
+        <v>1112</v>
+      </c>
+      <c r="E156" t="n">
+        <v>4</v>
+      </c>
+      <c r="F156" t="n">
         <v>2359</v>
       </c>
-      <c r="E156" t="n">
+      <c r="G156" t="n">
         <v>2331</v>
       </c>
-      <c r="F156" t="n">
+      <c r="H156" t="n">
         <v>1287</v>
       </c>
-      <c r="G156" t="n">
+      <c r="I156" t="n">
         <v>231191.3</v>
       </c>
-      <c r="H156" t="n">
+      <c r="J156" t="n">
         <v>226657.4</v>
       </c>
-      <c r="I156" t="n">
+      <c r="K156" t="n">
         <v>134096.6</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8395,7 +9529,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ZAC_zzx/results/fourway/四方法对比_硬层.xlsx
+++ b/ZAC_zzx/results/fourway/四方法对比_硬层.xlsx
@@ -461,7 +461,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Num. Rearr. Steps 为真值（ICCAD'25 Table I 同口径：一次完整 AOD 重排循环=1步；ZAC/遗传=rearrangeJob 条数）。遗传两席=GA初始化+鬼点硬保证层（前瞻席=鬼点罚 w_ghost=1）；ICCAD=astar 优先回落 agnostic；同架构同判分器。</t>
+          <t>Num. Rearr. Steps 为真值（ICCAD'25 Table I 同口径：一次完整 AOD 重排循环=1步；ZAC/遗传=rearrangeJob 条数）。遗传两席=GA初始化+鬼点硬保证层（前瞻席=鬼点罚 w_ghost=1）；ICCAD=astar 优先回落 agnostic；同架构同判分器。注意：本表 ICCAD 列用四方统一预处理（qiskit 转译 cz/u 基、opt=1）——与论文 Table I 的复现管线（u1/u2 基、opt=3，见 experiments/results/qmap_qasmbench.csv，步数 13/15 与论文精确一致）是两种口径；差异全部来自转译层（如 ising 论文口径 9 步、本表 8 步；seca 81 vs 89），架构与编译器参数逐项核对相同。</t>
         </is>
       </c>
     </row>
